--- a/TrapchumApp/wwwroot/Reports/Schedule.xlsx
+++ b/TrapchumApp/wwwroot/Reports/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KhDev\Blazors\trapchum\TCLMS.Server\wwwroot\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KhDev\2025\LoanManagementSystem\TrapchumApp\wwwroot\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC34F73-EE87-4476-BA4C-7761036EC807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85386048-CAE6-454E-BE63-B594CDA56D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="666" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>ទ្រព្យជុំ ឃែស ផន សប</t>
   </si>
@@ -129,9 +129,6 @@
     <t>17-12-2021</t>
   </si>
   <si>
-    <t>ប្រាក់ប្រសិទ្ធភាព</t>
-  </si>
-  <si>
     <t>060S141</t>
   </si>
   <si>
@@ -156,18 +153,12 @@
     <t>{{l.LoanOutstanding}}</t>
   </si>
   <si>
-    <t>{{l.Principal}}</t>
-  </si>
-  <si>
     <t>{{totalDay}}</t>
   </si>
   <si>
     <t>{{principle}}</t>
   </si>
   <si>
-    <t>{{l.CollectionFee}}</t>
-  </si>
-  <si>
     <t>{{name}}</t>
   </si>
   <si>
@@ -196,6 +187,9 @@
   </si>
   <si>
     <t>{{phone}}</t>
+  </si>
+  <si>
+    <t>{{l.Principle}}</t>
   </si>
 </sst>
 </file>
@@ -460,10 +454,9 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="justify"/>
     </xf>
@@ -475,8 +468,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -495,23 +488,17 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -520,10 +507,10 @@
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -553,9 +540,6 @@
     <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -565,7 +549,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -580,9 +564,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -598,10 +579,10 @@
     <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -628,13 +609,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -643,7 +624,7 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -680,8 +661,8 @@
       <xdr:rowOff>114023</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>190501</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>472441</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
@@ -994,471 +975,454 @@
   <dimension ref="B1:M76"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.44140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="16.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="2:13" s="1" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.8">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="2:13" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-    </row>
-    <row r="5" spans="2:13" s="6" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="2:13" s="8" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="2:13" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="55" t="s">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="2:13" s="5" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="2:13" s="7" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-    </row>
-    <row r="8" spans="2:13" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="55" t="s">
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="33" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="24" t="str">
+      <c r="G8" s="21" t="str">
         <f>E23</f>
         <v>{{principle}}</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" spans="2:13" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="55" t="s">
+      <c r="I8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="56" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="51"/>
+      <c r="F9" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="60"/>
+      <c r="F10" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="M10" s="10"/>
+    </row>
+    <row r="11" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="61"/>
+      <c r="F11" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="14"/>
+      <c r="M11" s="10"/>
+    </row>
+    <row r="12" spans="2:13" s="1" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:13" s="1" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="2:13" s="15" customFormat="1" ht="24.6" x14ac:dyDescent="0.85">
+      <c r="B15" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="57"/>
+      <c r="E15" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" s="17" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="33" t="s">
+      <c r="C16" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="37">
+        <v>11</v>
+      </c>
+      <c r="C17" s="38">
+        <v>44267</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="37">
+        <v>12</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+    </row>
+    <row r="19" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="45"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="37"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="45"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="37">
+        <v>13</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="45"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="2:10" s="17" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="37">
         <v>14</v>
       </c>
-      <c r="G9" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="2:13" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="65" t="s">
+      <c r="C22" s="38"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="42">
+        <v>100000</v>
+      </c>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="45"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="2:10" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B23" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="M10" s="11"/>
-    </row>
-    <row r="11" spans="2:13" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="15"/>
-      <c r="M11" s="11"/>
-    </row>
-    <row r="12" spans="2:13" s="1" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="2:13" s="1" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="2:13" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="2:13" s="16" customFormat="1" ht="24.6" x14ac:dyDescent="0.85">
-      <c r="B15" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" s="18" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="44" t="s">
+      <c r="G23" s="45"/>
+      <c r="H23" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="2:10" s="4" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="2:10" s="4" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="C25" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="58"/>
+      <c r="I25" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" s="4" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="I26" s="28"/>
+    </row>
+    <row r="27" spans="2:10" s="18" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" s="3" customFormat="1" ht="24.6" x14ac:dyDescent="0.85">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B29" s="4"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8">
+      <c r="B30" s="18"/>
+      <c r="C30" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="21"/>
-    </row>
-    <row r="17" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="41">
-        <v>11</v>
-      </c>
-      <c r="C17" s="42">
-        <v>44267</v>
-      </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="49"/>
-      <c r="K17" s="17"/>
-    </row>
-    <row r="18" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="41">
-        <v>12</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="49"/>
-    </row>
-    <row r="19" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="50"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="41"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="50"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="41">
-        <v>13</v>
-      </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="50"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="2:11" s="18" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="41">
-        <v>14</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47">
-        <v>100000</v>
-      </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="50"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="2:11" s="5" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B23" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="2:11" s="5" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B24" s="25"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="2:11" s="5" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="C25" s="63" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="63"/>
-      <c r="E25" s="36"/>
-      <c r="I25" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" s="5" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="36"/>
-      <c r="I26" s="31"/>
-    </row>
-    <row r="27" spans="2:11" s="19" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-    </row>
-    <row r="28" spans="2:11" s="4" customFormat="1" ht="24.6" x14ac:dyDescent="0.85">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-    </row>
-    <row r="29" spans="2:11" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B29" s="5"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="5"/>
-    </row>
-    <row r="30" spans="2:11" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8">
-      <c r="B30" s="19"/>
-      <c r="C30" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" s="32"/>
-    </row>
-    <row r="31" spans="2:11" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
-    <row r="32" spans="2:11" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="29"/>
+    </row>
+    <row r="31" spans="2:10" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
+    <row r="32" spans="2:10" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="33" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="34" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="35" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
@@ -1469,8 +1433,8 @@
     </row>
     <row r="37" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="38" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8">
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
     </row>
     <row r="39" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="40" spans="2:3" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
@@ -1510,8 +1474,8 @@
     <row r="74" spans="4:5" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="75" spans="4:5" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8"/>
     <row r="76" spans="4:5" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8">
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="D76"/>
+      <c r="E76"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/TrapchumApp/wwwroot/Reports/Schedule.xlsx
+++ b/TrapchumApp/wwwroot/Reports/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KhDev\2025\LoanManagementSystem\TrapchumApp\wwwroot\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85386048-CAE6-454E-BE63-B594CDA56D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B296B964-5255-4D2B-BF89-462B8E4BE8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="666" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,12 +591,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -607,24 +625,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -992,43 +992,43 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="2:13" s="1" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.8">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="2:13" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="2:13" s="5" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
       <c r="B5" s="6"/>
@@ -1053,10 +1053,10 @@
       <c r="J6" s="8"/>
     </row>
     <row r="7" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="50"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="35" t="s">
         <v>40</v>
       </c>
@@ -1064,22 +1064,22 @@
       <c r="F7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51" t="s">
+      <c r="C8" s="54"/>
+      <c r="D8" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="51"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="30" t="s">
         <v>13</v>
       </c>
@@ -1096,14 +1096,14 @@
       <c r="J8" s="14"/>
     </row>
     <row r="9" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51" t="s">
+      <c r="C9" s="54"/>
+      <c r="D9" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="51"/>
+      <c r="E9" s="55"/>
       <c r="F9" s="30" t="s">
         <v>14</v>
       </c>
@@ -1119,14 +1119,14 @@
       <c r="J9" s="14"/>
     </row>
     <row r="10" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="60" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="60"/>
+      <c r="E10" s="56"/>
       <c r="F10" s="30" t="s">
         <v>15</v>
       </c>
@@ -1141,14 +1141,14 @@
       <c r="M10" s="10"/>
     </row>
     <row r="11" spans="2:13" s="11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="61" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="61"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="30" t="s">
         <v>16</v>
       </c>
@@ -1204,10 +1204,10 @@
       <c r="B15" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="57"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="36" t="s">
         <v>5</v>
       </c>
@@ -1360,10 +1360,10 @@
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="2:10" s="4" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="58"/>
+      <c r="D25" s="52"/>
       <c r="I25" s="4" t="s">
         <v>8</v>
       </c>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="30" spans="2:10" s="1" customFormat="1" ht="22.8" x14ac:dyDescent="0.8">
       <c r="B30" s="18"/>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="59"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
@@ -1479,6 +1479,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C30:D30"/>
@@ -1488,13 +1495,6 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="G7:J7"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.17" bottom="0.19" header="0.17" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
